--- a/docs/concept-v0.1.xlsx
+++ b/docs/concept-v0.1.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>要件定義書 ver.1.00</t>
+          <t>要件定義書 ver.1.01</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -956,112 +956,156 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr"/>
+    </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  学期の入れ替え(F10)では、Claude Code が「管理用の小さな命令」を使って、終わった授業の入れ物を終了にする。データのファイルを直接いじらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>部品と決めたこと</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>部品</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>決めたこと</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>要件定義との対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>本体</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Python(Flask)で作る。02_開発 のほかのツールと同じ作り方。Outlook を読む部品(pywin32)は入っている</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>制約 C6</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Chrome の専用の窓(アドレス欄やタブのない、workbench だけの細い窓)で開く。窓を閉じても本体は動き続ける。デスクトップに「作業台を開く」を置き、窓を開き直せる</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>利用場面、F3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>自動で動き出す仕組み</t>
+          <t>本体</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>タスクスケジューラに「ログインしたら動かす」「止まったら動かし直す」と登録する。登録は実装のときに Claude が行い、schtasks の確認の命令で本当に登録されたかを確かめる</t>
+          <t>Python(Flask)で作る。02_開発 のほかのツールと同じ作り方。Outlook を読む部品(pywin32)は入っている</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>制約 C6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>データの置き場所</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>data/ の中の SQLite のファイル1つにまとめる。公開リポジトリには入れない</t>
+          <t>Chrome の専用の窓(アドレス欄やタブのない、workbench だけの細い窓)で開く。窓を閉じても本体は動き続ける。デスクトップに「作業台を開く」を置き、窓を開き直せる(Claude の案:窓を閉じても本体は動き続ける/デスクトップの「作業台を開く」)</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>非機能 データ・安全</t>
+          <t>利用場面、F3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
+          <t>自動で動き出す仕組み</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>タスクスケジューラに「ログインしたら動かす」「止まったら動かし直す」と登録する。登録は実装のときに Claude が行い、schtasks の確認の命令で本当に登録されたかを確かめる</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>データの置き場所</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>data/ の中の SQLite のファイル1つにまとめる。公開リポジトリには入れない</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>非機能 データ・安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>鍵の置き場所</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Google の合鍵と通行証は、2つとも .env に置く。通行証が新しくなったら本体が .env を書き直す。.env は公開リポジトリに入れない</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Google の合鍵と通行証は、2つとも .env に置く。通行証が新しくなったら本体が .env を書き直す。.env は公開リポジトリに入れない(Claude の案:通行証が新しくなったら本体が .env を書き直す)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>非機能 27行目</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>管理用の小さな命令</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>本体に、入れ物の終了などを行う小さな命令を用意する。学期の入れ替えのとき、Claude Code がこれを使う(F10)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>外からの接続</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>本体は、この PC の中(localhost)からの接続だけを受け付ける。同じ Wi-Fi のほかの端末からは開けない</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>非機能 外から使えないこと</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1194,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>F3 F4 F6 F8 F10 F12 F16 F17 F18</t>
+          <t>F2 F3 F4 F6 F7 F8 F9 F10 F11 F12 F13 F16 F17 F18 F19 F20</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1216,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>F13 F14 F19</t>
+          <t>F10 F13 F14 F19</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1277,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>タスク、作業記録の手直し、git のコミット、開発の中身と進み具合</t>
+          <t>タスク、作業記録の手直し、git のコミット、開発の中身と進み具合。就活の企業の入れ物では、企業のメールアドレスもここで登録する</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>F2 F5 F7 F15</t>
+          <t>F2 F5 F7 F11 F15</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1304,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>F1 F14 F20</t>
+          <t>F1 F8 F9 F11 F12 F13 F14 F20</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1325,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>新しい連絡があるときは、帯の「連絡」のボタンに赤い点をつける(トップの2段目の「新しい連絡 ○件」と合わせて目印を二重にする)。</t>
+          <t>新しい連絡があるときは、帯の「連絡」のボタンに赤い点をつける(Claude の案。トップの2段目の「新しい連絡 ○件」と合わせて目印を二重にする)。</t>
         </is>
       </c>
     </row>
@@ -1289,6 +1333,20 @@
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>トップでは、スケジュールはその日の予定(今日の時間)、連絡は件数の目印だけを見せ、詳しくはそれぞれの画面に移って見る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>作業の切り替え(非機能:2クリック以内)は、トップの1段目から、入れ物とタスクを選んで開始する形で守る。細かい押し方は基本設計で確かめる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>トップは先に画面を出し、取り込みは裏で続ける。取り込み中は2段目に「読み込み中」と出す(非機能:2秒以内)。</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1389,7 +1447,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>名前・種類・終了したか・トップに出すか・リポジトリ・企業のアドレス</t>
+          <t>名前・種類・終了したか・トップに出すか・リポジトリ・企業のアドレス・開発の中身の一言と選んだ状態(F15)</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1411,7 +1469,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>名前・締切・着手日・繰り返し・完了・「自動」の印・メールから入った印</t>
+          <t>名前・入れ物・締切・着手日・繰り返し・完了・「自動」の印・メールから入った印・「Claude が読み取った」印</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1450,12 +1508,12 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>取り込んだ連絡</t>
+          <t>コミット</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>件名・差出人・日付・分類・振り分け先・リンク・「見た」・本文</t>
+          <t>手の記録にくっつかなかったコミット(その時刻に何をしたかの点。作業時間には数えない。F7)</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1465,19 +1523,19 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>本文だけ90日(Claude の案)で消す。件名などは残す</t>
+          <t>ずっと残す</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>覚えておくもの</t>
+          <t>取り込んだ連絡</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>振り分けの覚え・消したものの記録・バイト先の一覧・シフト表での自分の名前・大学のアドレス</t>
+          <t>件名・差出人・日付・分類・振り分け先・リンク・「見た」・本文</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1487,19 +1545,19 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>ずっと残す</t>
+          <t>本文だけ90日(Claude の案)で消す。件名などは残す</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>預かった予定</t>
+          <t>覚えておくもの</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Google カレンダーに書けなかった予定</t>
+          <t>振り分けの覚え・消したものの記録・バイト先の一覧・シフト表での自分の名前・大学のアドレス</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1509,63 +1567,107 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>書けたら、または「書かない」を選んだら消す</t>
+          <t>ずっと残す</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>予定の本体</t>
+          <t>預かった予定</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Google カレンダーの予定</t>
+          <t>Google カレンダーに書けなかった予定</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Google カレンダー</t>
+          <t>data/ の SQLite</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>workbench には写しを持たない(F19)</t>
+          <t>書けたら、または「書かない」を選んだら消す</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
+          <t>スケジュールの付け足し</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Google の予定ごとに workbench だけが持つもの:入っている入れ物・招待された予定のトグル・メールから入った印・目印つきの締切の予定とタスクの結びつき</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>data/ の SQLite</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>予定が Google から消えたら消す(細かい動きは基本設計)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>予定の本体</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Google カレンダーの予定</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Google カレンダー</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>予定そのものの写しは持たない(F19)。付け足しだけを持つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>鍵</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Google の合鍵と通行証</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>公開リポジトリに入れない</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>本文を90日で消した連絡を開いたときは、Outlook や Gmail を読みに行く。読めないときは「本文は90日で消えています。Outlook で開いてください」と出す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>本文を90日で消した連絡を開いたときは、Outlook や Gmail を読みに行く(Claude の案)。読めないときは「本文は90日で消えています。Outlook または Gmail で開いてください」と出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>締切やリンクは、取り込むときにタスクや連絡に写しておくので、本文を消しても困らない。</t>
         </is>
@@ -1586,7 +1688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1619,7 +1721,7 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>メールの取り込み(起動時と10分ごと)</t>
+          <t>メールの取り込み(起動時と10分ごと。10分は Claude の案)</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1760,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Outlook(大学)と Gmail(企業・アルバイト)のメールを読む</t>
+          <t>Outlook(大学)と Gmail(企業・アルバイト)のメールを読む。取り込み中は2段目に「読み込み中」と出す</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1724,7 +1826,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>3 で見つからないが「締切」「期限」「面接」などの言葉があるメールだけ、本文から締切・面接日を読み取る。読み取ったものには「Claude が読み取った」印をつける</t>
+          <t>3 で見つからないが「締切」「〆切」「期限」「提出」「面接」「面談」のどれかがあるメールだけ、本文から締切・面接日を読み取る。読み取ったものには「Claude が読み取った」印をつける</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -1746,7 +1848,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>タスク・スケジュールにし、「メールから自動で入った」印をつける</t>
+          <t>タスク・スケジュールにし、「メールから自動で入った」印をつける。提出受付のメールなら、そのタスクを自動で完了にする(F18 ①)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1768,7 +1870,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Google カレンダーに目印つきで書く。書けなければ預かる</t>
+          <t>Google カレンダーに目印つきで書く。「その他」のメールから入ったものは書かない。書けなければ預かる</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -2123,6 +2225,313 @@
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>git の取り込み(起動時と10分ごと。10分は Claude の案)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>だれが</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>AI 呼び出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>登録したリポジトリの新しいコミットを読む</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>変更されたフォルダで入れ物に振り分ける</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>同じ入れ物の手の記録が動いていればくっつけ、なければ点として残す</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>メッセージに「完了: タスク名」があれば、そのタスクを自動で完了にする(F18 ②)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>終わっていそうの判断(1日1回、朝)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>だれが</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>AI 呼び出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>まだ完了していないタスクと、最近のメール・コミット・作業記録をまとめる</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>終わっていそうなタスクを選ぶ(F18 ④)</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>claude -p</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>2段目に「終わっていそう ○件」と出す。自分が「完了」を押す</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>学期の入れ替え(学期の終わりに、自分が Claude に頼んだとき)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>だれが</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>AI 呼び出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>自分</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>新しい時間割を Claude に説明する</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>timetable.md を書き換え、管理用の小さな命令で終わった授業の入れ物を終了にする。何をどう変えたかを説明する</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Claude Code(会話)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>次に時間割を読んだとき、新しい授業の入れ物を作る</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -2386,7 +2795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2551,7 +2960,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>①の間はメールもカレンダーもつながっていないので、締切は自分で入れる。その間はモーニングブリーフと並べて使う。</t>
+          <t>①の間はメールもカレンダーもつながっていないので、締切は自分で入れる。その間はモーニングブリーフと並べて使う。(Claude の案)</t>
         </is>
       </c>
     </row>
@@ -2626,6 +3035,18 @@
       <c r="B20" s="10" t="inlineStr">
         <is>
           <t>UI 試作</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Google の合鍵は、実装のときに本人が Google の画面で作る(Claude の案。手順は Claude が伝える)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>実装</t>
         </is>
       </c>
     </row>

--- a/docs/concept-v0.1.xlsx
+++ b/docs/concept-v0.1.xlsx
@@ -1325,7 +1325,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>新しい連絡があるときは、帯の「連絡」のボタンに赤い点をつける(Claude の案。トップの2段目の「新しい連絡 ○件」と合わせて目印を二重にする)。</t>
+          <t>新しい連絡があるときは、帯の「連絡」のボタンに青い点をつける(本人が青に決めた。トップの2段目の「新しい連絡 ○件」と合わせて目印を二重にする)。</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>2段目に「新しい連絡 ○件」を出し、帯の「連絡」に赤い点をつける</t>
+          <t>2段目に「新しい連絡 ○件」を出し、帯の「連絡」に青い点をつける</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">

--- a/docs/concept-v0.1.xlsx
+++ b/docs/concept-v0.1.xlsx
@@ -1311,7 +1311,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>画面の行き来:画面の一番下に5つのボタン(トップ・予定・連絡・入れ物・設定)を並べた帯を置く。押すのは1回。</t>
+          <t>画面の行き来:画面の一番下に5つのボタン(トップ・予定・連絡・入れ物・設定)を並べた帯を置く。押すのは1回。「予定」は「スケジュール」の画面の短い呼び名。</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>本文だけ90日(Claude の案)で消す。件名などは残す</t>
+          <t>本文だけ90日で消す。件名などは残す</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>預かった予定</t>
+          <t>出せなかった通知</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Google カレンダーに書けなかった予定</t>
+          <t>PC の電源が切れていた間に出すはずだった通知(F8)</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1589,85 +1589,129 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>書けたら、または「書かない」を選んだら消す</t>
+          <t>次に画面を開いて見せたら消す</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>スケジュールの付け足し</t>
+          <t>シフト表の写真と読み取った結果</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Google の予定ごとに workbench だけが持つもの:入っている入れ物・招待された予定のトグル・メールから入った印・目印つきの締切の予定とタスクの結びつき</t>
+          <t>落とした写真と、Claude が読み取った結果(ほかのスタッフの分を含む)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>data/ の SQLite</t>
+          <t>残さない(読み取りの間だけ使う)</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>予定が Google から消えたら消す(細かい動きは基本設計)</t>
+          <t>「書き込む」を押したら、または小窓を閉じたら消す。写真も残さない(写真を残さないのは Claude の案)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>予定の本体</t>
+          <t>預かった予定</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Google カレンダーの予定</t>
+          <t>Google カレンダーに書けなかった予定。作る順番の②の間(カレンダーがまだつながっていない間)にメールから入った面接日・休講・補講もここに入れる</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Google カレンダー</t>
+          <t>data/ の SQLite</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>予定そのものの写しは持たない(F19)。付け足しだけを持つ</t>
+          <t>書けたら、または「書かない」を選んだら消す</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>スケジュールの付け足し</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Google の予定ごとに workbench だけが持つもの:入っている入れ物・招待された予定のトグル・メールから入った印・「Claude が読み取った」印・目印つきの締切の予定とタスクの結びつき</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>data/ の SQLite</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>予定が Google から消えたら消す(細かい動きは基本設計)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>予定の本体</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Google カレンダーの予定</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Google カレンダー</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>予定そのものの写しは持たない(F19)。付け足しだけを持つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
           <t>鍵</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Google の合鍵と通行証</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>.env</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>公開リポジトリに入れない</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>本文を90日で消した連絡を開いたときは、Outlook や Gmail を読みに行く(Claude の案)。読めないときは「本文は90日で消えています。Outlook または Gmail で開いてください」と出す。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>締切やリンクは、取り込むときにタスクや連絡に写しておくので、本文を消しても困らない。</t>
         </is>
@@ -1688,7 +1732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1782,7 +1826,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>差出人と科目名・企業名で、入れ物と分類を決める</t>
+          <t>差出人・科目名・企業名・バイト先の一覧(F20)・選び直した結果の覚え(F9・F11)で、入れ物と分類を決める</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -1826,7 +1870,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>3 で見つからないが「締切」「〆切」「期限」「提出」「面接」「面談」のどれかがあるメールだけ、本文から締切・面接日を読み取る。読み取ったものには「Claude が読み取った」印をつける</t>
+          <t>3 で見つからないが「締切」「〆切」「期限」「提出」「面接」「面談」のどれかがあるメールだけ、本文から締切・面接日を読み取る。読み取ったものには「Claude が読み取った」印をつける。Claude が動かない・読めないときは、2段目④の「読めなかった」に出す(細かい出し方は基本設計)</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -2350,7 +2394,7 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>終わっていそうの判断(1日1回、朝)</t>
+          <t>終わっていそうの判断(1日1回。その日、最初に PC を使い始めたとき)</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2433,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>まだ完了していないタスクと、最近のメール・コミット・作業記録をまとめる</t>
+          <t>まだ完了していないタスクと、前回の判断から後のメール・コミット・作業記録をまとめる</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -2532,6 +2576,240 @@
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Google カレンダーと時間割を読む(起動時と10分ごと。10分は Claude の案)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>だれが</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>AI 呼び出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>時間割ファイル timetable.md を読み、今日の授業を出す(F10)</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Google カレンダーの予定を読む(F12・F19)</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>目印つきの締切の予定が Google 側で動いていたら、タスクの締切を合わせる(F13)</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>預かった予定があれば、Google カレンダーに書き直す</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>トップの「今日の時間」とスケジュールの画面に出す</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>通知(1分ごとに確かめる。1分は Claude の案)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>だれが</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>AI 呼び出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>締切の前日・手つかず・2時間続いた記録・着手日を過ぎた、を確かめる(F8・F16)</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>当てはまれば Windows の通知を出し、トップにも出す</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>本体</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>PC の電源が切れていて出せなかった通知は、出せなかった通知として残し、次に画面を開いたときにまとめて見せる</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
@@ -2705,7 +2983,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>読むだけ。公開リポジトリには入れない</t>
+          <t>読むだけ(起動時と10分ごと)。学期の入れ替えのときだけ Claude Code が書き換える。公開リポジトリには入れない</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -2727,7 +3005,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>シフト表の写真、締切の読み取り(決まった書き方で見つからないときだけ)、終わっていそうの判断</t>
+          <t>シフト表の写真、締切・面接日の読み取り(決まった書き方で見つからないときだけ)、終わっていそうの判断(1日1回)、学期の入れ替え(会話で頼んだとき。管理用の小さな命令を使う)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2795,7 +3073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2971,41 +3249,36 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>②の間は Google カレンダーがまだつながっていないので、メールから入った面接日・休講・補講は「預かった予定」に入れ、トップの「今日の時間」には出す。③ができたら、まとめて Google カレンダーに書く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>次の工程で決めること</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>こと</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>いつ決めるか</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>data/ の SQLite のファイルの予備(バックアップ)の取り方</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>基本設計</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>「Claude が読み取った」印の見た目</t>
+          <t>data/ の SQLite のファイルの予備(バックアップ)の取り方</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3017,7 +3290,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>設定の画面の「本体が動いているか」の表示</t>
+          <t>「Claude が読み取った」印の見た目</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -3029,22 +3302,34 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>下の帯の高さと文字</t>
+          <t>設定の画面の「本体が動いているか」の表示</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>UI 試作</t>
+          <t>基本設計</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
+          <t>下の帯の高さと文字</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>UI 試作</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
           <t>Google の合鍵は、実装のときに本人が Google の画面で作る(Claude の案。手順は Claude が伝える)</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>実装</t>
         </is>
